--- a/docs/v/SAM-daily-latest.xlsx
+++ b/docs/v/SAM-daily-latest.xlsx
@@ -8,16 +8,16 @@
   </bookViews>
   <sheets>
     <sheet name="Daily Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Day 2026-10-11" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Day 2026-10-12" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="All Notices" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="First Seen By Day" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Run Log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Summary'!$A$1:$E$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Day 2026-10-11'!$A$1:$Q$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Notices'!$A$1:$Q$158</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'First Seen By Day'!$A$1:$Q$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Day 2026-10-12'!$A$1:$Q$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Notices'!$A$1:$Q$156</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'First Seen By Day'!$A$1:$Q$156</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -534,7 +534,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -544,116 +544,116 @@
         <v>50</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -663,14 +663,14 @@
         <v>61</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -680,48 +680,48 @@
         <v>61</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
@@ -731,31 +731,31 @@
         <v>66</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
@@ -765,7 +765,7 @@
         <v>62</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" s="3" t="inlineStr"/>
     </row>
@@ -893,7 +893,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr"/>
@@ -957,14 +957,14 @@
       </c>
       <c r="Q2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr"/>
@@ -1024,14 +1024,14 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr"/>
@@ -1095,14 +1095,14 @@
       </c>
       <c r="Q4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr"/>
@@ -1162,14 +1162,14 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr"/>
@@ -1233,14 +1233,14 @@
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr"/>
@@ -1304,14 +1304,14 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr"/>
@@ -1375,14 +1375,14 @@
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr"/>
@@ -1446,14 +1446,14 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr"/>
@@ -1517,14 +1517,14 @@
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr"/>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr"/>
@@ -1655,14 +1655,14 @@
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr"/>
@@ -1726,14 +1726,14 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr"/>
@@ -1793,14 +1793,14 @@
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr"/>
@@ -1864,14 +1864,14 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr"/>
@@ -1935,14 +1935,14 @@
       </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr"/>
@@ -2002,14 +2002,14 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr"/>
@@ -2073,14 +2073,14 @@
       </c>
       <c r="Q18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr"/>
@@ -2144,14 +2144,14 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr"/>
@@ -2215,14 +2215,14 @@
       </c>
       <c r="Q20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr"/>
@@ -2286,14 +2286,14 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr"/>
@@ -2357,14 +2357,14 @@
       </c>
       <c r="Q22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr"/>
@@ -2428,14 +2428,14 @@
       </c>
       <c r="Q23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr"/>
@@ -2499,14 +2499,14 @@
       </c>
       <c r="Q24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr"/>
@@ -2570,14 +2570,14 @@
       </c>
       <c r="Q25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr"/>
@@ -2641,14 +2641,14 @@
       </c>
       <c r="Q26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr"/>
@@ -2712,14 +2712,14 @@
       </c>
       <c r="Q27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr"/>
@@ -2779,14 +2779,14 @@
       </c>
       <c r="Q28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr"/>
@@ -2850,14 +2850,14 @@
       </c>
       <c r="Q29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr"/>
@@ -2921,14 +2921,14 @@
       </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr"/>
@@ -2992,14 +2992,14 @@
       </c>
       <c r="Q31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr"/>
@@ -3063,14 +3063,14 @@
       </c>
       <c r="Q32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr"/>
@@ -3134,14 +3134,14 @@
       </c>
       <c r="Q33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr"/>
@@ -3205,14 +3205,14 @@
       </c>
       <c r="Q34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr"/>
@@ -3276,14 +3276,14 @@
       </c>
       <c r="Q35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr"/>
@@ -3347,14 +3347,14 @@
       </c>
       <c r="Q36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr"/>
@@ -3418,14 +3418,14 @@
       </c>
       <c r="Q37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr"/>
@@ -3489,14 +3489,14 @@
       </c>
       <c r="Q38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr"/>
@@ -3560,14 +3560,14 @@
       </c>
       <c r="Q39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr"/>
@@ -3627,14 +3627,14 @@
       </c>
       <c r="Q40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr"/>
@@ -3698,14 +3698,14 @@
       </c>
       <c r="Q41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr"/>
@@ -3765,14 +3765,14 @@
       </c>
       <c r="Q42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr"/>
@@ -3836,14 +3836,14 @@
       </c>
       <c r="Q43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr"/>
@@ -3903,14 +3903,14 @@
       </c>
       <c r="Q44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr"/>
@@ -3974,14 +3974,14 @@
       </c>
       <c r="Q45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr"/>
@@ -4041,14 +4041,14 @@
       </c>
       <c r="Q46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr"/>
@@ -4112,14 +4112,14 @@
       </c>
       <c r="Q47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr"/>
@@ -4183,14 +4183,14 @@
       </c>
       <c r="Q48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr"/>
@@ -4254,14 +4254,14 @@
       </c>
       <c r="Q49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr"/>
@@ -4325,14 +4325,14 @@
       </c>
       <c r="Q50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr"/>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="Q51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q158"/>
+  <dimension ref="A1:Q156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4576,7 +4576,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr"/>
@@ -4640,14 +4640,14 @@
       </c>
       <c r="Q2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr"/>
@@ -4707,14 +4707,14 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr"/>
@@ -4778,14 +4778,14 @@
       </c>
       <c r="Q4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr"/>
@@ -4845,14 +4845,14 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr"/>
@@ -4916,14 +4916,14 @@
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr"/>
@@ -4987,14 +4987,14 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr"/>
@@ -5058,14 +5058,14 @@
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr"/>
@@ -5129,14 +5129,14 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr"/>
@@ -5196,14 +5196,14 @@
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr"/>
@@ -5267,14 +5267,14 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr"/>
@@ -5334,14 +5334,14 @@
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr"/>
@@ -5405,14 +5405,14 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr"/>
@@ -5476,14 +5476,14 @@
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr"/>
@@ -5547,14 +5547,14 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr"/>
@@ -5618,14 +5618,14 @@
       </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr"/>
@@ -5689,14 +5689,14 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr"/>
@@ -5760,14 +5760,14 @@
       </c>
       <c r="Q18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr"/>
@@ -5831,14 +5831,14 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr"/>
@@ -5898,14 +5898,14 @@
       </c>
       <c r="Q20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr"/>
@@ -5969,14 +5969,14 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr"/>
@@ -6040,14 +6040,14 @@
       </c>
       <c r="Q22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr"/>
@@ -6111,14 +6111,14 @@
       </c>
       <c r="Q23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr"/>
@@ -6182,14 +6182,14 @@
       </c>
       <c r="Q24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr"/>
@@ -6253,14 +6253,14 @@
       </c>
       <c r="Q25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr"/>
@@ -6324,14 +6324,14 @@
       </c>
       <c r="Q26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr"/>
@@ -6395,14 +6395,14 @@
       </c>
       <c r="Q27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr"/>
@@ -6462,14 +6462,14 @@
       </c>
       <c r="Q28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr"/>
@@ -6533,14 +6533,14 @@
       </c>
       <c r="Q29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr"/>
@@ -6604,14 +6604,14 @@
       </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr"/>
@@ -6675,14 +6675,14 @@
       </c>
       <c r="Q31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr"/>
@@ -6746,14 +6746,14 @@
       </c>
       <c r="Q32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr"/>
@@ -6817,14 +6817,14 @@
       </c>
       <c r="Q33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr"/>
@@ -6888,14 +6888,14 @@
       </c>
       <c r="Q34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr"/>
@@ -6959,14 +6959,14 @@
       </c>
       <c r="Q35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr"/>
@@ -7030,14 +7030,14 @@
       </c>
       <c r="Q36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr"/>
@@ -7101,14 +7101,14 @@
       </c>
       <c r="Q37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr"/>
@@ -7172,14 +7172,14 @@
       </c>
       <c r="Q38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr"/>
@@ -7243,14 +7243,14 @@
       </c>
       <c r="Q39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr"/>
@@ -7310,14 +7310,14 @@
       </c>
       <c r="Q40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr"/>
@@ -7377,14 +7377,14 @@
       </c>
       <c r="Q41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr"/>
@@ -7448,14 +7448,14 @@
       </c>
       <c r="Q42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr"/>
@@ -7519,14 +7519,14 @@
       </c>
       <c r="Q43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr"/>
@@ -7590,14 +7590,14 @@
       </c>
       <c r="Q44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr"/>
@@ -7657,14 +7657,14 @@
       </c>
       <c r="Q45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr"/>
@@ -7724,14 +7724,14 @@
       </c>
       <c r="Q46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr"/>
@@ -7795,14 +7795,14 @@
       </c>
       <c r="Q47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr"/>
@@ -7866,14 +7866,14 @@
       </c>
       <c r="Q48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr"/>
@@ -7937,14 +7937,14 @@
       </c>
       <c r="Q49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr"/>
@@ -8008,14 +8008,14 @@
       </c>
       <c r="Q50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr"/>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="Q51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -15482,150 +15482,8 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr"/>
-      <c r="C157" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="D157" s="4" t="inlineStr">
-        <is>
-          <t>SAP Software Subscription, Maintenance, and SAP N2 Cloud Hosting</t>
-        </is>
-      </c>
-      <c r="E157" s="5" t="inlineStr">
-        <is>
-          <t>https://sam.gov/opp/7262f257e0f5428fba1fb038998f5b36/view</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>IRS</t>
-        </is>
-      </c>
-      <c r="G157" s="4" t="inlineStr">
-        <is>
-          <t>Sources Sought</t>
-        </is>
-      </c>
-      <c r="H157" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-02T16:00:00+00:00</t>
-        </is>
-      </c>
-      <c r="I157" s="4" t="inlineStr">
-        <is>
-          <t>IRS27-220503</t>
-        </is>
-      </c>
-      <c r="J157" s="4" t="inlineStr"/>
-      <c r="K157" s="4" t="inlineStr">
-        <is>
-          <t>TREASURY, DEPARTMENT OF THE.INTERNAL REVENUE SERVICE.NATIONAL OFFICE - PROCUREMENT OITA</t>
-        </is>
-      </c>
-      <c r="L157" s="4" t="inlineStr"/>
-      <c r="M157" s="4" t="inlineStr"/>
-      <c r="N157" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O157" s="4" t="inlineStr">
-        <is>
-          <t>7262f257e0f5428fba1fb038998f5b36</t>
-        </is>
-      </c>
-      <c r="P157" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Q157" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="inlineStr"/>
-      <c r="C158" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="D158" s="4" t="inlineStr">
-        <is>
-          <t>Ball Bearings</t>
-        </is>
-      </c>
-      <c r="E158" s="5" t="inlineStr">
-        <is>
-          <t>https://sam.gov/opp/0c69761d169749fea4a45bc5ac38cce9/view</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>Cyber</t>
-        </is>
-      </c>
-      <c r="G158" s="4" t="inlineStr">
-        <is>
-          <t>Combined Synopsis/Solicitation</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06T17:00:00+00:00</t>
-        </is>
-      </c>
-      <c r="I158" s="4" t="inlineStr">
-        <is>
-          <t>W5119TC26QBAL1</t>
-        </is>
-      </c>
-      <c r="J158" s="4" t="inlineStr"/>
-      <c r="K158" s="4" t="inlineStr">
-        <is>
-          <t>DEPT OF DEFENSE.DEPT OF THE ARMY.AMC.ACC.ACC-CTRS.ACC RI.W6QK ACC-RI</t>
-        </is>
-      </c>
-      <c r="L158" s="4" t="inlineStr"/>
-      <c r="M158" s="4" t="inlineStr"/>
-      <c r="N158" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O158" s="4" t="inlineStr">
-        <is>
-          <t>0c69761d169749fea4a45bc5ac38cce9</t>
-        </is>
-      </c>
-      <c r="P158" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q158" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q158"/>
+  <autoFilter ref="A1:Q156"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -15782,8 +15640,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId153"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId157"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15795,7 +15651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q158"/>
+  <dimension ref="A1:Q156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15967,7 +15823,7 @@
       </c>
       <c r="Q2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -16038,7 +15894,7 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -16109,7 +15965,7 @@
       </c>
       <c r="Q4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -16180,7 +16036,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -16247,7 +16103,7 @@
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -16318,7 +16174,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -16389,7 +16245,7 @@
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -16456,7 +16312,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -16527,7 +16383,7 @@
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -16598,7 +16454,7 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -16669,7 +16525,7 @@
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -16740,7 +16596,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -16811,7 +16667,7 @@
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -16878,7 +16734,7 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -16945,7 +16801,7 @@
       </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -17016,7 +16872,7 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -17087,7 +16943,7 @@
       </c>
       <c r="Q18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -17158,7 +17014,7 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -17371,7 +17227,7 @@
       </c>
       <c r="Q22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -17442,7 +17298,7 @@
       </c>
       <c r="Q23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17369,7 @@
       </c>
       <c r="Q24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -17584,7 +17440,7 @@
       </c>
       <c r="Q25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -17655,7 +17511,7 @@
       </c>
       <c r="Q26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -17797,7 +17653,7 @@
       </c>
       <c r="Q28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -17939,7 +17795,7 @@
       </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -18010,7 +17866,7 @@
       </c>
       <c r="Q31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -18081,7 +17937,7 @@
       </c>
       <c r="Q32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -18152,7 +18008,7 @@
       </c>
       <c r="Q33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -18223,7 +18079,7 @@
       </c>
       <c r="Q34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -18294,7 +18150,7 @@
       </c>
       <c r="Q35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -18365,7 +18221,7 @@
       </c>
       <c r="Q36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -18507,7 +18363,7 @@
       </c>
       <c r="Q38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18434,7 @@
       </c>
       <c r="Q39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -18645,7 +18501,7 @@
       </c>
       <c r="Q40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -18716,7 +18572,7 @@
       </c>
       <c r="Q41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -18787,7 +18643,7 @@
       </c>
       <c r="Q42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -18858,7 +18714,7 @@
       </c>
       <c r="Q43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -19000,7 +18856,7 @@
       </c>
       <c r="Q45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -19067,7 +18923,7 @@
       </c>
       <c r="Q46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -19138,7 +18994,7 @@
       </c>
       <c r="Q47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19065,7 @@
       </c>
       <c r="Q48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -19347,7 +19203,7 @@
       </c>
       <c r="Q50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -19485,7 +19341,7 @@
       </c>
       <c r="Q52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -19836,7 +19692,7 @@
       </c>
       <c r="Q57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -20747,7 +20603,7 @@
       </c>
       <c r="Q70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -21173,7 +21029,7 @@
       </c>
       <c r="Q76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21455,7 @@
       </c>
       <c r="Q82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -22092,7 +21948,7 @@
       </c>
       <c r="Q89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -22301,7 +22157,7 @@
       </c>
       <c r="Q92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -22443,7 +22299,7 @@
       </c>
       <c r="Q94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -23443,38 +23299,38 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>SAP Software Subscription, Maintenance, and SAP N2 Cloud Hosting</t>
+          <t>Notice of Intent to Sole Source -Bode Cellmark Forensics</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/7262f257e0f5428fba1fb038998f5b36/view</t>
+          <t>https://sam.gov/opp/53d3fc22ebe34e04bf68d5eae26eb259/view</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>Forensic; Forensics</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>Sources Sought</t>
+          <t>Presolicitation</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T16:00:00+00:00</t>
+          <t>2026-10-08T14:00:00+00:00</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>IRS27-220503</t>
+          <t>PANDHA-26-P-0000046460</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr"/>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>TREASURY, DEPARTMENT OF THE.INTERNAL REVENUE SERVICE.NATIONAL OFFICE - PROCUREMENT OITA</t>
+          <t>DEPT OF DEFENSE.DEFENSE HEALTH AGENCY (DHA).ARMY MED RES ACQ ACTIVITY</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr"/>
@@ -23486,7 +23342,7 @@
       </c>
       <c r="O109" s="4" t="inlineStr">
         <is>
-          <t>7262f257e0f5428fba1fb038998f5b36</t>
+          <t>53d3fc22ebe34e04bf68d5eae26eb259</t>
         </is>
       </c>
       <c r="P109" s="4" t="inlineStr">
@@ -23496,7 +23352,7 @@
       </c>
       <c r="Q109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -23514,38 +23370,38 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Notice of Intent to Sole Source -Bode Cellmark Forensics</t>
+          <t>Mission Assurance Services (A Dept.)</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/53d3fc22ebe34e04bf68d5eae26eb259/view</t>
+          <t>https://sam.gov/opp/aae63948c3f04422a0a4ab9095526209/view</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>Forensic; Forensics</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Sources Sought</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T14:00:00+00:00</t>
+          <t>2026-10-06T16:00:00+00:00</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
-          <t>PANDHA-26-P-0000046460</t>
+          <t>N0017827R4405</t>
         </is>
       </c>
       <c r="J110" s="4" t="inlineStr"/>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>DEPT OF DEFENSE.DEFENSE HEALTH AGENCY (DHA).ARMY MED RES ACQ ACTIVITY</t>
+          <t>DEPT OF DEFENSE.DEPT OF THE NAVY.NAVSEA.NAVSEA WARFARE CENTER.NSWC DAHLGREN</t>
         </is>
       </c>
       <c r="L110" s="4" t="inlineStr"/>
@@ -23557,7 +23413,7 @@
       </c>
       <c r="O110" s="4" t="inlineStr">
         <is>
-          <t>53d3fc22ebe34e04bf68d5eae26eb259</t>
+          <t>aae63948c3f04422a0a4ab9095526209</t>
         </is>
       </c>
       <c r="P110" s="4" t="inlineStr">
@@ -23567,7 +23423,7 @@
       </c>
       <c r="Q110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23585,12 +23441,12 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Mission Assurance Services (A Dept.)</t>
+          <t>GEN6 V006 CYBER SCAN</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/aae63948c3f04422a0a4ab9095526209/view</t>
+          <t>https://sam.gov/opp/eca2a97b8f764ab6864e0771e42aab0a/view</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
@@ -23600,23 +23456,23 @@
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>Sources Sought</t>
+          <t>Presolicitation</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T16:00:00+00:00</t>
+          <t>2026-10-09T18:00:00+00:00</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>N0017827R4405</t>
+          <t>N00421-26-RFPREQ-TPM209-0513</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr"/>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>DEPT OF DEFENSE.DEPT OF THE NAVY.NAVSEA.NAVSEA WARFARE CENTER.NSWC DAHLGREN</t>
+          <t>DEPT OF DEFENSE.DEPT OF THE NAVY.NAVAIR.NAVAIR NAWC AD.NAVAL AIR WARFARE CENTER AIR DIV</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr"/>
@@ -23628,7 +23484,7 @@
       </c>
       <c r="O111" s="4" t="inlineStr">
         <is>
-          <t>aae63948c3f04422a0a4ab9095526209</t>
+          <t>eca2a97b8f764ab6864e0771e42aab0a</t>
         </is>
       </c>
       <c r="P111" s="4" t="inlineStr">
@@ -23656,38 +23512,38 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>GEN6 V006 CYBER SCAN</t>
+          <t>Forensic Laptops</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/eca2a97b8f764ab6864e0771e42aab0a/view</t>
+          <t>https://sam.gov/opp/e835ac7597804441bcba3c56ab8baeee/view</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>Forensic</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T18:00:00+00:00</t>
+          <t>2026-09-25T21:00:00+00:00</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
-          <t>N00421-26-RFPREQ-TPM209-0513</t>
+          <t>0020154457</t>
         </is>
       </c>
       <c r="J112" s="4" t="inlineStr"/>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>DEPT OF DEFENSE.DEPT OF THE NAVY.NAVAIR.NAVAIR NAWC AD.NAVAL AIR WARFARE CENTER AIR DIV</t>
+          <t>HOMELAND SECURITY, DEPARTMENT OF.U.S. CUSTOMS AND BORDER PROTECTION.INFORMATION TECHNOLOGY CONTRACTING DIVISION</t>
         </is>
       </c>
       <c r="L112" s="4" t="inlineStr"/>
@@ -23699,7 +23555,7 @@
       </c>
       <c r="O112" s="4" t="inlineStr">
         <is>
-          <t>eca2a97b8f764ab6864e0771e42aab0a</t>
+          <t>e835ac7597804441bcba3c56ab8baeee</t>
         </is>
       </c>
       <c r="P112" s="4" t="inlineStr">
@@ -23709,7 +23565,7 @@
       </c>
       <c r="Q112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -23727,38 +23583,38 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Forensic Laptops</t>
+          <t>FY27 Mentor Protege Program (MPP) Broad Agency Announcement</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/e835ac7597804441bcba3c56ab8baeee/view</t>
+          <t>https://sam.gov/opp/ba442a223ba3431180476179c4941cba/view</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>Forensic</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>Solicitation</t>
+          <t>Combined Synopsis/Solicitation</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T21:00:00+00:00</t>
+          <t>2027-08-01T05:01:00+00:00</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>0020154457</t>
+          <t>MPP-FY2027</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr"/>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>HOMELAND SECURITY, DEPARTMENT OF.U.S. CUSTOMS AND BORDER PROTECTION.INFORMATION TECHNOLOGY CONTRACTING DIVISION</t>
+          <t>DEPT OF DEFENSE.DEPT OF THE ARMY.AMC.ACC.ACC-CTRS.ACC-APG.W6QK ACC-APG</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr"/>
@@ -23770,7 +23626,7 @@
       </c>
       <c r="O113" s="4" t="inlineStr">
         <is>
-          <t>e835ac7597804441bcba3c56ab8baeee</t>
+          <t>ba442a223ba3431180476179c4941cba</t>
         </is>
       </c>
       <c r="P113" s="4" t="inlineStr">
@@ -23780,7 +23636,7 @@
       </c>
       <c r="Q113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -23798,12 +23654,12 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>FY27 Mentor Protege Program (MPP) Broad Agency Announcement</t>
+          <t>Cyber Assessment Support</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/ba442a223ba3431180476179c4941cba/view</t>
+          <t>https://sam.gov/opp/466f18ac92be4e6ca14a73778ec99ff8/view</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
@@ -23813,27 +23669,27 @@
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>Combined Synopsis/Solicitation</t>
-        </is>
-      </c>
-      <c r="H114" s="4" t="inlineStr">
-        <is>
-          <t>2027-08-01T05:01:00+00:00</t>
-        </is>
-      </c>
+          <t>Award Notice</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr"/>
       <c r="I114" s="4" t="inlineStr">
         <is>
-          <t>MPP-FY2027</t>
+          <t>W9124226PA039</t>
         </is>
       </c>
       <c r="J114" s="4" t="inlineStr"/>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>DEPT OF DEFENSE.DEPT OF THE ARMY.AMC.ACC.ACC-CTRS.ACC-APG.W6QK ACC-APG</t>
+          <t>DEPT OF DEFENSE.DEPT OF THE ARMY.NGB.W7NS USPFO ACTIVITY NC ARNG</t>
         </is>
       </c>
       <c r="L114" s="4" t="inlineStr"/>
-      <c r="M114" s="4" t="inlineStr"/>
+      <c r="M114" s="4" t="inlineStr">
+        <is>
+          <t>ERUDIO CORP</t>
+        </is>
+      </c>
       <c r="N114" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -23841,7 +23697,7 @@
       </c>
       <c r="O114" s="4" t="inlineStr">
         <is>
-          <t>ba442a223ba3431180476179c4941cba</t>
+          <t>466f18ac92be4e6ca14a73778ec99ff8</t>
         </is>
       </c>
       <c r="P114" s="4" t="inlineStr">
@@ -23869,12 +23725,12 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Cyber Assessment Support</t>
+          <t>Contract Opportunity Network Enabled Weapons Trainer (NEWT)</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/466f18ac92be4e6ca14a73778ec99ff8/view</t>
+          <t>https://sam.gov/opp/5cda2f44503648df82fbb8b5f6cff4ea/view</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
@@ -23884,27 +23740,27 @@
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>Award Notice</t>
-        </is>
-      </c>
-      <c r="H115" s="4" t="inlineStr"/>
+          <t>Sources Sought</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-09T22:00:00+00:00</t>
+        </is>
+      </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>W9124226PA039</t>
+          <t>N00019-25-RFPREQ-WPM201-0360</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr"/>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>DEPT OF DEFENSE.DEPT OF THE ARMY.NGB.W7NS USPFO ACTIVITY NC ARNG</t>
+          <t>DEPT OF DEFENSE.DEPT OF THE NAVY.NAVAIR.NAVAIR HQS.NAVAL AIR SYSTEMS COMMAND</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr"/>
-      <c r="M115" s="4" t="inlineStr">
-        <is>
-          <t>ERUDIO CORP</t>
-        </is>
-      </c>
+      <c r="M115" s="4" t="inlineStr"/>
       <c r="N115" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -23912,7 +23768,7 @@
       </c>
       <c r="O115" s="4" t="inlineStr">
         <is>
-          <t>466f18ac92be4e6ca14a73778ec99ff8</t>
+          <t>5cda2f44503648df82fbb8b5f6cff4ea</t>
         </is>
       </c>
       <c r="P115" s="4" t="inlineStr">
@@ -23940,12 +23796,12 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Contract Opportunity Network Enabled Weapons Trainer (NEWT)</t>
+          <t>7A21--VISN Radiology Artificial Intelligence</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/5cda2f44503648df82fbb8b5f6cff4ea/view</t>
+          <t>https://sam.gov/opp/b57dd8cce65843449d426c5b38913470/view</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
@@ -23960,18 +23816,18 @@
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>2026-11-09T22:00:00+00:00</t>
+          <t>2026-02-13T15:00:00+00:00</t>
         </is>
       </c>
       <c r="I116" s="4" t="inlineStr">
         <is>
-          <t>N00019-25-RFPREQ-WPM201-0360</t>
+          <t>36C24126Q0237</t>
         </is>
       </c>
       <c r="J116" s="4" t="inlineStr"/>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>DEPT OF DEFENSE.DEPT OF THE NAVY.NAVAIR.NAVAIR HQS.NAVAL AIR SYSTEMS COMMAND</t>
+          <t>VETERANS AFFAIRS, DEPARTMENT OF.VETERANS AFFAIRS, DEPARTMENT OF.241-NETWORK CONTRACT OFFICE 01 (36C241)</t>
         </is>
       </c>
       <c r="L116" s="4" t="inlineStr"/>
@@ -23983,7 +23839,7 @@
       </c>
       <c r="O116" s="4" t="inlineStr">
         <is>
-          <t>5cda2f44503648df82fbb8b5f6cff4ea</t>
+          <t>b57dd8cce65843449d426c5b38913470</t>
         </is>
       </c>
       <c r="P116" s="4" t="inlineStr">
@@ -23993,14 +23849,14 @@
       </c>
       <c r="Q116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr"/>
@@ -24011,12 +23867,12 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>7A21--VISN Radiology Artificial Intelligence</t>
+          <t>RRS/DFAS Grounds MXS and Snow Removal</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/b57dd8cce65843449d426c5b38913470/view</t>
+          <t>https://sam.gov/opp/2389287f718143598b37f3c41de29d06/view</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
@@ -24026,23 +23882,23 @@
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>Sources Sought</t>
+          <t>Combined Synopsis/Solicitation</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13T15:00:00+00:00</t>
+          <t>2026-10-06T16:00:00+00:00</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>36C24126Q0237</t>
+          <t>FA875126Q0907</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr"/>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>VETERANS AFFAIRS, DEPARTMENT OF.VETERANS AFFAIRS, DEPARTMENT OF.241-NETWORK CONTRACT OFFICE 01 (36C241)</t>
+          <t>DEPT OF DEFENSE.DEPT OF THE AIR FORCE.AIR FORCE MATERIEL COMMAND.AIR FORCE RESEARCH LABORATORY.FA8751  AFRL RIKO</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr"/>
@@ -24054,12 +23910,12 @@
       </c>
       <c r="O117" s="4" t="inlineStr">
         <is>
-          <t>b57dd8cce65843449d426c5b38913470</t>
+          <t>2389287f718143598b37f3c41de29d06</t>
         </is>
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="Q117" s="4" t="inlineStr">
@@ -24082,38 +23938,38 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>RRS/DFAS Grounds MXS and Snow Removal</t>
+          <t>PEO-M Unmanned Surface Vehicle (USV) Poseidon's Fury Assessment Event (AE)</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/2389287f718143598b37f3c41de29d06/view</t>
+          <t>https://sam.gov/opp/11215d725f4846e296fcdede82e45696/view</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>SOFWERX</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>Combined Synopsis/Solicitation</t>
+          <t>Special Notice</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T16:00:00+00:00</t>
+          <t>2026-10-08T03:59:00+00:00</t>
         </is>
       </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
-          <t>FA875126Q0907</t>
+          <t>PEO_M_USV_Poseidons_Fury_AE</t>
         </is>
       </c>
       <c r="J118" s="4" t="inlineStr"/>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>DEPT OF DEFENSE.DEPT OF THE AIR FORCE.AIR FORCE MATERIEL COMMAND.AIR FORCE RESEARCH LABORATORY.FA8751  AFRL RIKO</t>
+          <t>DEPT OF DEFENSE</t>
         </is>
       </c>
       <c r="L118" s="4" t="inlineStr"/>
@@ -24125,7 +23981,7 @@
       </c>
       <c r="O118" s="4" t="inlineStr">
         <is>
-          <t>2389287f718143598b37f3c41de29d06</t>
+          <t>11215d725f4846e296fcdede82e45696</t>
         </is>
       </c>
       <c r="P118" s="4" t="inlineStr">
@@ -24135,7 +23991,7 @@
       </c>
       <c r="Q118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -24148,43 +24004,43 @@
       <c r="B119" s="4" t="inlineStr"/>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>PEO-M Unmanned Surface Vehicle (USV) Poseidon's Fury Assessment Event (AE)</t>
+          <t>USS Patrick Gallagher (DDG-127) Custom Galley Table and Chair Covers</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/11215d725f4846e296fcdede82e45696/view</t>
+          <t>https://sam.gov/opp/691aecfa68b1467a97d47d986d4f9492/view</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>SOFWERX</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>Special Notice</t>
+          <t>Combined Synopsis/Solicitation</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T03:59:00+00:00</t>
+          <t>2026-10-01T12:00:00+00:00</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>PEO_M_USV_Poseidons_Fury_AE</t>
+          <t>N2678626Q0007</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr"/>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>DEPT OF DEFENSE</t>
+          <t>DEPT OF DEFENSE.DEPT OF THE NAVY.NAVSEA.NAVSEA SUPSHIP.SUP OF SHIPBUILDING CONV AND REPAIR</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr"/>
@@ -24196,7 +24052,7 @@
       </c>
       <c r="O119" s="4" t="inlineStr">
         <is>
-          <t>11215d725f4846e296fcdede82e45696</t>
+          <t>691aecfa68b1467a97d47d986d4f9492</t>
         </is>
       </c>
       <c r="P119" s="4" t="inlineStr">
@@ -24206,7 +24062,7 @@
       </c>
       <c r="Q119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -24224,12 +24080,12 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>USS Patrick Gallagher (DDG-127) Custom Galley Table and Chair Covers</t>
+          <t>U.S. Army Contracting Command – Sierra Army Depot (ACC-SIAD) Organic Industrial Base (OIB) Modernization Commercial Solutions Opening (CSO)</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/691aecfa68b1467a97d47d986d4f9492/view</t>
+          <t>https://sam.gov/opp/808fb9cebbf94b8ba9039ebad338f8f8/view</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
@@ -24239,23 +24095,23 @@
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>Combined Synopsis/Solicitation</t>
+          <t>Special Notice</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T12:00:00+00:00</t>
+          <t>2030-06-30T17:00:00+00:00</t>
         </is>
       </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
-          <t>N2678626Q0007</t>
+          <t>W912GY-25-S-C001</t>
         </is>
       </c>
       <c r="J120" s="4" t="inlineStr"/>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>DEPT OF DEFENSE.DEPT OF THE NAVY.NAVSEA.NAVSEA SUPSHIP.SUP OF SHIPBUILDING CONV AND REPAIR</t>
+          <t>DEPT OF DEFENSE.DEPT OF THE ARMY.AMC.ACC.ACC-CTRS.ACC WRN.W6QK SIAD CONTR OFF</t>
         </is>
       </c>
       <c r="L120" s="4" t="inlineStr"/>
@@ -24267,7 +24123,7 @@
       </c>
       <c r="O120" s="4" t="inlineStr">
         <is>
-          <t>691aecfa68b1467a97d47d986d4f9492</t>
+          <t>808fb9cebbf94b8ba9039ebad338f8f8</t>
         </is>
       </c>
       <c r="P120" s="4" t="inlineStr">
@@ -24277,7 +24133,7 @@
       </c>
       <c r="Q120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -24295,38 +24151,38 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>U.S. Army Contracting Command – Sierra Army Depot (ACC-SIAD) Organic Industrial Base (OIB) Modernization Commercial Solutions Opening (CSO)</t>
+          <t>Request for Information: United States Coast Guard Core Navigation Software</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/808fb9cebbf94b8ba9039ebad338f8f8/view</t>
+          <t>https://sam.gov/opp/8be33d409c1e4759bbace84041738022/view</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>Forensic; Forensics</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>Special Notice</t>
+          <t>Sources Sought</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>2030-06-30T17:00:00+00:00</t>
+          <t>2026-10-23T21:00:00+00:00</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>W912GY-25-S-C001</t>
+          <t>70Z04427IOTI32721</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr"/>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>DEPT OF DEFENSE.DEPT OF THE ARMY.AMC.ACC.ACC-CTRS.ACC WRN.W6QK SIAD CONTR OFF</t>
+          <t>HOMELAND SECURITY, DEPARTMENT OF.U.S. COAST GUARD.C5I DIVISION 3 PORTSMOUTH</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr"/>
@@ -24338,7 +24194,7 @@
       </c>
       <c r="O121" s="4" t="inlineStr">
         <is>
-          <t>808fb9cebbf94b8ba9039ebad338f8f8</t>
+          <t>8be33d409c1e4759bbace84041738022</t>
         </is>
       </c>
       <c r="P121" s="4" t="inlineStr">
@@ -24348,7 +24204,7 @@
       </c>
       <c r="Q121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -24366,38 +24222,38 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Request for Information: United States Coast Guard Core Navigation Software</t>
+          <t>Notice of Intent to Sole Source to Isotropx</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/8be33d409c1e4759bbace84041738022/view</t>
+          <t>https://sam.gov/opp/b44d31a2829e42f29e0b0ab5e637906b/view</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>Forensic; Forensics</t>
+          <t>Forensics</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>Sources Sought</t>
+          <t>Presolicitation</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T21:00:00+00:00</t>
+          <t>2026-09-29T03:59:00+00:00</t>
         </is>
       </c>
       <c r="I122" s="4" t="inlineStr">
         <is>
-          <t>70Z04427IOTI32721</t>
+          <t>89243226QNE000030</t>
         </is>
       </c>
       <c r="J122" s="4" t="inlineStr"/>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>HOMELAND SECURITY, DEPARTMENT OF.U.S. COAST GUARD.C5I DIVISION 3 PORTSMOUTH</t>
+          <t>ENERGY, DEPARTMENT OF.ENERGY, DEPARTMENT OF.IDAHO OPERATIONS OFFICE</t>
         </is>
       </c>
       <c r="L122" s="4" t="inlineStr"/>
@@ -24409,7 +24265,7 @@
       </c>
       <c r="O122" s="4" t="inlineStr">
         <is>
-          <t>8be33d409c1e4759bbace84041738022</t>
+          <t>b44d31a2829e42f29e0b0ab5e637906b</t>
         </is>
       </c>
       <c r="P122" s="4" t="inlineStr">
@@ -24437,38 +24293,34 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Notice of Intent to Sole Source to Isotropx</t>
+          <t>7E--Forensic Workstation &amp; Laptops for OJS PCU</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/b44d31a2829e42f29e0b0ab5e637906b/view</t>
+          <t>https://sam.gov/opp/1ceaa431953742e4bda7be4746bc3cbc/view</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>Forensics</t>
+          <t>Forensic</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="H123" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-29T03:59:00+00:00</t>
-        </is>
-      </c>
+          <t>Justification</t>
+        </is>
+      </c>
+      <c r="H123" s="4" t="inlineStr"/>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>89243226QNE000030</t>
+          <t>140A0826P0014</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr"/>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>ENERGY, DEPARTMENT OF.ENERGY, DEPARTMENT OF.IDAHO OPERATIONS OFFICE</t>
+          <t>INTERIOR, DEPARTMENT OF THE.BUREAU OF INDIAN AFFAIRS.EASTERN OKLAHOMA REGION</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr"/>
@@ -24480,7 +24332,7 @@
       </c>
       <c r="O123" s="4" t="inlineStr">
         <is>
-          <t>b44d31a2829e42f29e0b0ab5e637906b</t>
+          <t>1ceaa431953742e4bda7be4746bc3cbc</t>
         </is>
       </c>
       <c r="P123" s="4" t="inlineStr">
@@ -24497,7 +24349,7 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr"/>
@@ -24508,38 +24360,42 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>7E--Forensic Workstation &amp; Laptops for OJS PCU</t>
+          <t>Z--HVAC REFURBISHMENT CU-9_NHOTIC for the BLM Vale Di</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/1ceaa431953742e4bda7be4746bc3cbc/view</t>
+          <t>https://sam.gov/opp/74e0b50f3f694ddb9ed1333a8abc6051/view</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>Forensic</t>
+          <t>Axiom</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>Justification</t>
+          <t>Award Notice</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
       <c r="I124" s="4" t="inlineStr">
         <is>
-          <t>140A0826P0014</t>
+          <t>140L4326R0032</t>
         </is>
       </c>
       <c r="J124" s="4" t="inlineStr"/>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>INTERIOR, DEPARTMENT OF THE.BUREAU OF INDIAN AFFAIRS.EASTERN OKLAHOMA REGION</t>
+          <t>INTERIOR, DEPARTMENT OF THE.BUREAU OF LAND MANAGEMENT.OREGON STATE OFFICE</t>
         </is>
       </c>
       <c r="L124" s="4" t="inlineStr"/>
-      <c r="M124" s="4" t="inlineStr"/>
+      <c r="M124" s="4" t="inlineStr">
+        <is>
+          <t>AXIOM BUILDERS INC</t>
+        </is>
+      </c>
       <c r="N124" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -24547,17 +24403,17 @@
       </c>
       <c r="O124" s="4" t="inlineStr">
         <is>
-          <t>1ceaa431953742e4bda7be4746bc3cbc</t>
+          <t>74e0b50f3f694ddb9ed1333a8abc6051</t>
         </is>
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -24570,47 +24426,47 @@
       <c r="B125" s="4" t="inlineStr"/>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Z--HVAC REFURBISHMENT CU-9_NHOTIC for the BLM Vale Di</t>
+          <t>Terrestrial Layered System (TLS) Manpack; Request for Information</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/74e0b50f3f694ddb9ed1333a8abc6051/view</t>
+          <t>https://sam.gov/opp/418b58d559874ea9ab3b3e52f8b42bbc/view</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Axiom</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>Award Notice</t>
-        </is>
-      </c>
-      <c r="H125" s="4" t="inlineStr"/>
+          <t>Sources Sought</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02T20:00:00+00:00</t>
+        </is>
+      </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>140L4326R0032</t>
+          <t>W56KGY-26-R-0099</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr"/>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>INTERIOR, DEPARTMENT OF THE.BUREAU OF LAND MANAGEMENT.OREGON STATE OFFICE</t>
+          <t>DEPT OF DEFENSE.DEPT OF THE ARMY.AMC.ACC.ACC-CTRS.ACC-APG.W6QK ACC-APG</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr"/>
-      <c r="M125" s="4" t="inlineStr">
-        <is>
-          <t>AXIOM BUILDERS INC</t>
-        </is>
-      </c>
+      <c r="M125" s="4" t="inlineStr"/>
       <c r="N125" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -24618,7 +24474,7 @@
       </c>
       <c r="O125" s="4" t="inlineStr">
         <is>
-          <t>74e0b50f3f694ddb9ed1333a8abc6051</t>
+          <t>418b58d559874ea9ab3b3e52f8b42bbc</t>
         </is>
       </c>
       <c r="P125" s="4" t="inlineStr">
@@ -24628,7 +24484,7 @@
       </c>
       <c r="Q125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -24646,12 +24502,12 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Terrestrial Layered System (TLS) Manpack; Request for Information</t>
+          <t>Request for Quotes: Independent Condition Assessment of Solar PV Systems Non-Personal Services</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/418b58d559874ea9ab3b3e52f8b42bbc/view</t>
+          <t>https://sam.gov/opp/27e43f672d8c440285d97d0dad32642e/view</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
@@ -24661,23 +24517,23 @@
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>Sources Sought</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T20:00:00+00:00</t>
+          <t>2026-09-16T20:00:00+00:00</t>
         </is>
       </c>
       <c r="I126" s="4" t="inlineStr">
         <is>
-          <t>W56KGY-26-R-0099</t>
+          <t>W912LR26QA040</t>
         </is>
       </c>
       <c r="J126" s="4" t="inlineStr"/>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>DEPT OF DEFENSE.DEPT OF THE ARMY.AMC.ACC.ACC-CTRS.ACC-APG.W6QK ACC-APG</t>
+          <t>DEPT OF DEFENSE.DEPT OF THE ARMY.NGB.W7PA USPFO ACTIVITY PR ARNG</t>
         </is>
       </c>
       <c r="L126" s="4" t="inlineStr"/>
@@ -24689,7 +24545,7 @@
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
-          <t>418b58d559874ea9ab3b3e52f8b42bbc</t>
+          <t>27e43f672d8c440285d97d0dad32642e</t>
         </is>
       </c>
       <c r="P126" s="4" t="inlineStr">
@@ -24717,38 +24573,38 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Request for Quotes: Independent Condition Assessment of Solar PV Systems Non-Personal Services</t>
+          <t>REQUEST FOR INFORMATION (RFI)/ SOURCES SOUGHT Space Force Mission Delta 9 (MD9) – SL-5 EC2-S Ground System Sustainment</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/27e43f672d8c440285d97d0dad32642e/view</t>
+          <t>https://sam.gov/opp/63826e3d171a4f228a888ce5cb72b5a1/view</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>Cyber; EC2</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>Solicitation</t>
+          <t>Sources Sought</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T20:00:00+00:00</t>
+          <t>2026-10-11T17:00:00+00:00</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>W912LR26QA040</t>
+          <t>RFI-MD9-2026-01</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr"/>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>DEPT OF DEFENSE.DEPT OF THE ARMY.NGB.W7PA USPFO ACTIVITY PR ARNG</t>
+          <t>DEPT OF DEFENSE.DEPT OF THE AIR FORCE.AIR FORCE SPACE COMMAND.FA2518  USSF SPOC/SAIO</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr"/>
@@ -24760,7 +24616,7 @@
       </c>
       <c r="O127" s="4" t="inlineStr">
         <is>
-          <t>27e43f672d8c440285d97d0dad32642e</t>
+          <t>63826e3d171a4f228a888ce5cb72b5a1</t>
         </is>
       </c>
       <c r="P127" s="4" t="inlineStr">
@@ -24770,7 +24626,7 @@
       </c>
       <c r="Q127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -24788,38 +24644,34 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>REQUEST FOR INFORMATION (RFI)/ SOURCES SOUGHT Space Force Mission Delta 9 (MD9) – SL-5 EC2-S Ground System Sustainment</t>
+          <t>PRECISELY RECOMPETE JEFO</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/63826e3d171a4f228a888ce5cb72b5a1/view</t>
+          <t>https://sam.gov/opp/7ae7dc858e8348e69d72c783dfd263d6/view</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>Cyber; EC2</t>
+          <t>IRS</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>Sources Sought</t>
-        </is>
-      </c>
-      <c r="H128" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-11T17:00:00+00:00</t>
-        </is>
-      </c>
+          <t>Justification</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr"/>
       <c r="I128" s="4" t="inlineStr">
         <is>
-          <t>RFI-MD9-2026-01</t>
+          <t>JEFO5000231516</t>
         </is>
       </c>
       <c r="J128" s="4" t="inlineStr"/>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>DEPT OF DEFENSE.DEPT OF THE AIR FORCE.AIR FORCE SPACE COMMAND.FA2518  USSF SPOC/SAIO</t>
+          <t>TREASURY, DEPARTMENT OF THE.INTERNAL REVENUE SERVICE.DEPT OF TREASURY IRS</t>
         </is>
       </c>
       <c r="L128" s="4" t="inlineStr"/>
@@ -24831,7 +24683,7 @@
       </c>
       <c r="O128" s="4" t="inlineStr">
         <is>
-          <t>63826e3d171a4f228a888ce5cb72b5a1</t>
+          <t>7ae7dc858e8348e69d72c783dfd263d6</t>
         </is>
       </c>
       <c r="P128" s="4" t="inlineStr">
@@ -24841,7 +24693,7 @@
       </c>
       <c r="Q128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -24859,38 +24711,46 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>PRECISELY RECOMPETE JEFO</t>
+          <t>Multiple Award Schedule</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/7ae7dc858e8348e69d72c783dfd263d6/view</t>
+          <t>https://sam.gov/opp/fd4539c9239448a0b7184e96db1d07e2/view</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>Justification</t>
-        </is>
-      </c>
-      <c r="H129" s="4" t="inlineStr"/>
+          <t>Award Notice</t>
+        </is>
+      </c>
+      <c r="H129" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22T16:12:13+00:00</t>
+        </is>
+      </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>JEFO5000231516</t>
+          <t>47QSMD20R0001</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr"/>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>TREASURY, DEPARTMENT OF THE.INTERNAL REVENUE SERVICE.DEPT OF TREASURY IRS</t>
+          <t>GENERAL SERVICES ADMINISTRATION.FEDERAL ACQUISITION SERVICE.GSA/FAS FURNITURE SYSTEMS MGT DIV</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr"/>
-      <c r="M129" s="4" t="inlineStr"/>
+      <c r="M129" s="4" t="inlineStr">
+        <is>
+          <t>CYBER INTELLIGENCE ALLIANCE LLC</t>
+        </is>
+      </c>
       <c r="N129" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -24898,7 +24758,7 @@
       </c>
       <c r="O129" s="4" t="inlineStr">
         <is>
-          <t>7ae7dc858e8348e69d72c783dfd263d6</t>
+          <t>fd4539c9239448a0b7184e96db1d07e2</t>
         </is>
       </c>
       <c r="P129" s="4" t="inlineStr">
@@ -24908,7 +24768,7 @@
       </c>
       <c r="Q129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -24926,46 +24786,42 @@
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Multiple Award Schedule</t>
+          <t>Mobile &amp; Data Services for the U.S. Embassy Panama</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/fd4539c9239448a0b7184e96db1d07e2/view</t>
+          <t>https://sam.gov/opp/6a56e054309545e5bd640d247ad3ed90/view</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>IRS</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>Award Notice</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T16:12:13+00:00</t>
+          <t>2026-10-13T20:00:00+00:00</t>
         </is>
       </c>
       <c r="I130" s="4" t="inlineStr">
         <is>
-          <t>47QSMD20R0001</t>
+          <t>19PM0726Q0012</t>
         </is>
       </c>
       <c r="J130" s="4" t="inlineStr"/>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>GENERAL SERVICES ADMINISTRATION.FEDERAL ACQUISITION SERVICE.GSA/FAS FURNITURE SYSTEMS MGT DIV</t>
+          <t>STATE, DEPARTMENT OF.STATE, DEPARTMENT OF.U.S. EMBASSY PANAMA CITY</t>
         </is>
       </c>
       <c r="L130" s="4" t="inlineStr"/>
-      <c r="M130" s="4" t="inlineStr">
-        <is>
-          <t>CYBER INTELLIGENCE ALLIANCE LLC</t>
-        </is>
-      </c>
+      <c r="M130" s="4" t="inlineStr"/>
       <c r="N130" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -24973,7 +24829,7 @@
       </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
-          <t>fd4539c9239448a0b7184e96db1d07e2</t>
+          <t>6a56e054309545e5bd640d247ad3ed90</t>
         </is>
       </c>
       <c r="P130" s="4" t="inlineStr">
@@ -24983,7 +24839,7 @@
       </c>
       <c r="Q130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -25001,38 +24857,34 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Mobile &amp; Data Services for the U.S. Embassy Panama</t>
+          <t>Magnet Graykey Licenses</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/6a56e054309545e5bd640d247ad3ed90/view</t>
+          <t>https://sam.gov/opp/a47ef701f14f4934a7b30e2011ec1f4b/view</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>GrayKey</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>Solicitation</t>
-        </is>
-      </c>
-      <c r="H131" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-13T20:00:00+00:00</t>
-        </is>
-      </c>
+          <t>Justification</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="inlineStr"/>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>19PM0726Q0012</t>
+          <t>DJA-26-ASOD-PR-0342</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr"/>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>STATE, DEPARTMENT OF.STATE, DEPARTMENT OF.U.S. EMBASSY PANAMA CITY</t>
+          <t>JUSTICE, DEPARTMENT OF.ATF ACQUISITION AND PROPERTY MGMT DIV.ATF</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr"/>
@@ -25044,7 +24896,7 @@
       </c>
       <c r="O131" s="4" t="inlineStr">
         <is>
-          <t>6a56e054309545e5bd640d247ad3ed90</t>
+          <t>a47ef701f14f4934a7b30e2011ec1f4b</t>
         </is>
       </c>
       <c r="P131" s="4" t="inlineStr">
@@ -25072,34 +24924,38 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Magnet Graykey Licenses</t>
+          <t>Laptops and Charging Carts</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/a47ef701f14f4934a7b30e2011ec1f4b/view</t>
+          <t>https://sam.gov/opp/902786ded77240f5a93d1328727e7235/view</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>GrayKey</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>Justification</t>
-        </is>
-      </c>
-      <c r="H132" s="4" t="inlineStr"/>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23T17:00:00+00:00</t>
+        </is>
+      </c>
       <c r="I132" s="4" t="inlineStr">
         <is>
-          <t>DJA-26-ASOD-PR-0342</t>
+          <t>HQ06426170902</t>
         </is>
       </c>
       <c r="J132" s="4" t="inlineStr"/>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>JUSTICE, DEPARTMENT OF.ATF ACQUISITION AND PROPERTY MGMT DIV.ATF</t>
+          <t>DEPT OF DEFENSE.DEPT OF THE AIR FORCE.AIR FORCE MATERIEL COMMAND.AIR FORCE TEST CENTER.FA9301  AFTC PZIO</t>
         </is>
       </c>
       <c r="L132" s="4" t="inlineStr"/>
@@ -25111,7 +24967,7 @@
       </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
-          <t>a47ef701f14f4934a7b30e2011ec1f4b</t>
+          <t>902786ded77240f5a93d1328727e7235</t>
         </is>
       </c>
       <c r="P132" s="4" t="inlineStr">
@@ -25121,7 +24977,7 @@
       </c>
       <c r="Q132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -25139,12 +24995,12 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Laptops and Charging Carts</t>
+          <t>Cloud-Based GRC / Cyber Risk Compliance Automation Platform (FISMA High SaaS)</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/902786ded77240f5a93d1328727e7235/view</t>
+          <t>https://sam.gov/opp/2d6c5ad85a5948b2b678d543bb2fa8d4/view</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
@@ -25159,18 +25015,18 @@
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T17:00:00+00:00</t>
+          <t>2026-09-28T15:00:00+00:00</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>HQ06426170902</t>
+          <t>GG000000-26-00063</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr"/>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>DEPT OF DEFENSE.DEPT OF THE AIR FORCE.AIR FORCE MATERIEL COMMAND.AIR FORCE TEST CENTER.FA9301  AFTC PZIO</t>
+          <t>COMMERCE, DEPARTMENT OF.OFFICE OF THE SECRETARY.DEPT OF COMMERCE ESO</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr"/>
@@ -25182,7 +25038,7 @@
       </c>
       <c r="O133" s="4" t="inlineStr">
         <is>
-          <t>902786ded77240f5a93d1328727e7235</t>
+          <t>2d6c5ad85a5948b2b678d543bb2fa8d4</t>
         </is>
       </c>
       <c r="P133" s="4" t="inlineStr">
@@ -25199,7 +25055,7 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr"/>
@@ -25210,12 +25066,12 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Cloud-Based GRC / Cyber Risk Compliance Automation Platform (FISMA High SaaS)</t>
+          <t>Space Warfighter Training, Modeling, and Simulation Support</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/2d6c5ad85a5948b2b678d543bb2fa8d4/view</t>
+          <t>https://sam.gov/opp/4004f21e9c8f410f96a7d43fa1a045c7/view</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
@@ -25225,25 +25081,21 @@
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>Solicitation</t>
+          <t>Sources Sought</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28T15:00:00+00:00</t>
+          <t>2026-10-08T16:00:00+00:00</t>
         </is>
       </c>
       <c r="I134" s="4" t="inlineStr">
         <is>
-          <t>GG000000-26-00063</t>
+          <t>FA254927R0002</t>
         </is>
       </c>
       <c r="J134" s="4" t="inlineStr"/>
-      <c r="K134" s="4" t="inlineStr">
-        <is>
-          <t>COMMERCE, DEPARTMENT OF.OFFICE OF THE SECRETARY.DEPT OF COMMERCE ESO</t>
-        </is>
-      </c>
+      <c r="K134" s="4" t="inlineStr"/>
       <c r="L134" s="4" t="inlineStr"/>
       <c r="M134" s="4" t="inlineStr"/>
       <c r="N134" s="4" t="inlineStr">
@@ -25253,17 +25105,17 @@
       </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
-          <t>2d6c5ad85a5948b2b678d543bb2fa8d4</t>
+          <t>4004f21e9c8f410f96a7d43fa1a045c7</t>
         </is>
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -25281,12 +25133,12 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Space Warfighter Training, Modeling, and Simulation Support</t>
+          <t>Persistent Cyber Training Environment Support Services</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/4004f21e9c8f410f96a7d43fa1a045c7/view</t>
+          <t>https://sam.gov/opp/fefcc8b820a544bbb67edcf99b34e577/view</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
@@ -25296,23 +25148,27 @@
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>Sources Sought</t>
-        </is>
-      </c>
-      <c r="H135" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08T16:00:00+00:00</t>
-        </is>
-      </c>
+          <t>Award Notice</t>
+        </is>
+      </c>
+      <c r="H135" s="4" t="inlineStr"/>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>FA254927R0002</t>
+          <t>N0018926PL364</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr"/>
-      <c r="K135" s="4" t="inlineStr"/>
+      <c r="K135" s="4" t="inlineStr">
+        <is>
+          <t>DEPT OF DEFENSE.DEPT OF THE NAVY.NAVSUP.NAVSUP GLOBAL LOGISTICS SUPPORT.NAVSUP FLC NORFOLK.NAVSUP FLT LOG CTR NORFOLK</t>
+        </is>
+      </c>
       <c r="L135" s="4" t="inlineStr"/>
-      <c r="M135" s="4" t="inlineStr"/>
+      <c r="M135" s="4" t="inlineStr">
+        <is>
+          <t>NEXAGEN NETWORKS, INC.</t>
+        </is>
+      </c>
       <c r="N135" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -25320,7 +25176,7 @@
       </c>
       <c r="O135" s="4" t="inlineStr">
         <is>
-          <t>4004f21e9c8f410f96a7d43fa1a045c7</t>
+          <t>fefcc8b820a544bbb67edcf99b34e577</t>
         </is>
       </c>
       <c r="P135" s="4" t="inlineStr">
@@ -25348,42 +25204,42 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Persistent Cyber Training Environment Support Services</t>
+          <t>PA-AEIF Summit Hotel accommodations and conference space</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/fefcc8b820a544bbb67edcf99b34e577/view</t>
+          <t>https://sam.gov/opp/701526aa557b401f882bdf3835605cb6/view</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>IRS</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>Award Notice</t>
-        </is>
-      </c>
-      <c r="H136" s="4" t="inlineStr"/>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24T09:00:00+00:00</t>
+        </is>
+      </c>
       <c r="I136" s="4" t="inlineStr">
         <is>
-          <t>N0018926PL364</t>
+          <t>19TS8026Q0016</t>
         </is>
       </c>
       <c r="J136" s="4" t="inlineStr"/>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>DEPT OF DEFENSE.DEPT OF THE NAVY.NAVSUP.NAVSUP GLOBAL LOGISTICS SUPPORT.NAVSUP FLC NORFOLK.NAVSUP FLT LOG CTR NORFOLK</t>
+          <t>STATE, DEPARTMENT OF.STATE, DEPARTMENT OF.U.S. EMBASSY TUNIS</t>
         </is>
       </c>
       <c r="L136" s="4" t="inlineStr"/>
-      <c r="M136" s="4" t="inlineStr">
-        <is>
-          <t>NEXAGEN NETWORKS, INC.</t>
-        </is>
-      </c>
+      <c r="M136" s="4" t="inlineStr"/>
       <c r="N136" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -25391,7 +25247,7 @@
       </c>
       <c r="O136" s="4" t="inlineStr">
         <is>
-          <t>fefcc8b820a544bbb67edcf99b34e577</t>
+          <t>701526aa557b401f882bdf3835605cb6</t>
         </is>
       </c>
       <c r="P136" s="4" t="inlineStr">
@@ -25401,7 +25257,7 @@
       </c>
       <c r="Q136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -25419,38 +25275,34 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>PA-AEIF Summit Hotel accommodations and conference space</t>
+          <t>Ground Vehicle System Center (GVSC) Commercial Solutions Opening (CSO)</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/701526aa557b401f882bdf3835605cb6/view</t>
+          <t>https://sam.gov/opp/62c084a672c04685b1bdb23febfdd05b/view</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>Solicitation</t>
-        </is>
-      </c>
-      <c r="H137" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-24T09:00:00+00:00</t>
-        </is>
-      </c>
+          <t>Special Notice</t>
+        </is>
+      </c>
+      <c r="H137" s="4" t="inlineStr"/>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>19TS8026Q0016</t>
+          <t>W912CH-24-S-0002</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr"/>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>STATE, DEPARTMENT OF.STATE, DEPARTMENT OF.U.S. EMBASSY TUNIS</t>
+          <t>DEPT OF DEFENSE.DEPT OF THE ARMY.AMC.ACC.ACC-CTRS.ACC WRN.W4GG HQ US ARMY TACOM</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr"/>
@@ -25462,7 +25314,7 @@
       </c>
       <c r="O137" s="4" t="inlineStr">
         <is>
-          <t>701526aa557b401f882bdf3835605cb6</t>
+          <t>62c084a672c04685b1bdb23febfdd05b</t>
         </is>
       </c>
       <c r="P137" s="4" t="inlineStr">
@@ -25472,7 +25324,7 @@
       </c>
       <c r="Q137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -25485,39 +25337,43 @@
       <c r="B138" s="4" t="inlineStr"/>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Ground Vehicle System Center (GVSC) Commercial Solutions Opening (CSO)</t>
+          <t>Software Licensing and Training</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/62c084a672c04685b1bdb23febfdd05b/view</t>
+          <t>https://sam.gov/opp/2701c90fc3264c22ba8bb5feb389ddb7/view</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>IRS</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>Special Notice</t>
-        </is>
-      </c>
-      <c r="H138" s="4" t="inlineStr"/>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23T13:00:00+00:00</t>
+        </is>
+      </c>
       <c r="I138" s="4" t="inlineStr">
         <is>
-          <t>W912CH-24-S-0002</t>
+          <t>2043FY-26-Q-00090</t>
         </is>
       </c>
       <c r="J138" s="4" t="inlineStr"/>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>DEPT OF DEFENSE.DEPT OF THE ARMY.AMC.ACC.ACC-CTRS.ACC WRN.W4GG HQ US ARMY TACOM</t>
+          <t>TREASURY, DEPARTMENT OF THE.INTERNAL REVENUE SERVICE.SOUTHEAST REGION</t>
         </is>
       </c>
       <c r="L138" s="4" t="inlineStr"/>
@@ -25529,7 +25385,7 @@
       </c>
       <c r="O138" s="4" t="inlineStr">
         <is>
-          <t>62c084a672c04685b1bdb23febfdd05b</t>
+          <t>2701c90fc3264c22ba8bb5feb389ddb7</t>
         </is>
       </c>
       <c r="P138" s="4" t="inlineStr">
@@ -25539,7 +25395,7 @@
       </c>
       <c r="Q138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -25557,38 +25413,38 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Software Licensing and Training</t>
+          <t>Sea Lice Genotyping</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/2701c90fc3264c22ba8bb5feb389ddb7/view</t>
+          <t>https://sam.gov/opp/4396670b2f2b423485b6f4e09a6f3d3f/view</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>Axiom</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>Solicitation</t>
+          <t>Combined Synopsis/Solicitation</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T13:00:00+00:00</t>
+          <t>2026-09-24T15:00:00+00:00</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>2043FY-26-Q-00090</t>
+          <t>Solicitation1232SA26Q1506</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr"/>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>TREASURY, DEPARTMENT OF THE.INTERNAL REVENUE SERVICE.SOUTHEAST REGION</t>
+          <t>AGRICULTURE, DEPARTMENT OF.FOREST SERVICE.USDA FOREST SERVICE</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr"/>
@@ -25600,7 +25456,7 @@
       </c>
       <c r="O139" s="4" t="inlineStr">
         <is>
-          <t>2701c90fc3264c22ba8bb5feb389ddb7</t>
+          <t>4396670b2f2b423485b6f4e09a6f3d3f</t>
         </is>
       </c>
       <c r="P139" s="4" t="inlineStr">
@@ -25628,38 +25484,34 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Sea Lice Genotyping</t>
+          <t>SPECIAL NOTICE: 91st Cyber Operations Center Progressive-Design-Build OT</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/4396670b2f2b423485b6f4e09a6f3d3f/view</t>
+          <t>https://sam.gov/opp/f6293a48b6124e0cb7521a0066c70eb3/view</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>Axiom</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>Combined Synopsis/Solicitation</t>
+          <t>Special Notice</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T15:00:00+00:00</t>
-        </is>
-      </c>
-      <c r="I140" s="4" t="inlineStr">
-        <is>
-          <t>Solicitation1232SA26Q1506</t>
-        </is>
-      </c>
+          <t>2026-10-02T15:02:00+00:00</t>
+        </is>
+      </c>
+      <c r="I140" s="4" t="inlineStr"/>
       <c r="J140" s="4" t="inlineStr"/>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>AGRICULTURE, DEPARTMENT OF.FOREST SERVICE.USDA FOREST SERVICE</t>
+          <t>DEPT OF DEFENSE.DEPT OF THE ARMY.USACE.SWD.W076 ENDIST FT WORTH</t>
         </is>
       </c>
       <c r="L140" s="4" t="inlineStr"/>
@@ -25671,7 +25523,7 @@
       </c>
       <c r="O140" s="4" t="inlineStr">
         <is>
-          <t>4396670b2f2b423485b6f4e09a6f3d3f</t>
+          <t>f6293a48b6124e0cb7521a0066c70eb3</t>
         </is>
       </c>
       <c r="P140" s="4" t="inlineStr">
@@ -25681,7 +25533,7 @@
       </c>
       <c r="Q140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -25699,12 +25551,12 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>SPECIAL NOTICE: 91st Cyber Operations Center Progressive-Design-Build OT</t>
+          <t>Medidata Remote Source Review (RSR)</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/f6293a48b6124e0cb7521a0066c70eb3/view</t>
+          <t>https://sam.gov/opp/8f8ea644341143e4b0365947421d57fc/view</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
@@ -25714,21 +25566,21 @@
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>Special Notice</t>
+          <t>Presolicitation</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T15:02:00+00:00</t>
-        </is>
-      </c>
-      <c r="I141" s="4" t="inlineStr"/>
+          <t>2026-09-30T00:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="I141" s="4" t="inlineStr">
+        <is>
+          <t>HHS-OMAS-2027-03</t>
+        </is>
+      </c>
       <c r="J141" s="4" t="inlineStr"/>
-      <c r="K141" s="4" t="inlineStr">
-        <is>
-          <t>DEPT OF DEFENSE.DEPT OF THE ARMY.USACE.SWD.W076 ENDIST FT WORTH</t>
-        </is>
-      </c>
+      <c r="K141" s="4" t="inlineStr"/>
       <c r="L141" s="4" t="inlineStr"/>
       <c r="M141" s="4" t="inlineStr"/>
       <c r="N141" s="4" t="inlineStr">
@@ -25738,7 +25590,7 @@
       </c>
       <c r="O141" s="4" t="inlineStr">
         <is>
-          <t>f6293a48b6124e0cb7521a0066c70eb3</t>
+          <t>8f8ea644341143e4b0365947421d57fc</t>
         </is>
       </c>
       <c r="P141" s="4" t="inlineStr">
@@ -25755,7 +25607,7 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr"/>
@@ -25766,36 +25618,40 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Medidata Remote Source Review (RSR)</t>
+          <t>Teledyne Griffin G510X Service Agreement</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/8f8ea644341143e4b0365947421d57fc/view</t>
+          <t>https://sam.gov/opp/7b57c68cd1c94196a4bc7d87b7824706/view</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>Forensic</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Combined Synopsis/Solicitation</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30T00:00:00+00:00</t>
+          <t>2026-09-24T19:00:00+00:00</t>
         </is>
       </c>
       <c r="I142" s="4" t="inlineStr">
         <is>
-          <t>HHS-OMAS-2027-03</t>
+          <t>75F40126Q00370</t>
         </is>
       </c>
       <c r="J142" s="4" t="inlineStr"/>
-      <c r="K142" s="4" t="inlineStr"/>
+      <c r="K142" s="4" t="inlineStr">
+        <is>
+          <t>HEALTH AND HUMAN SERVICES, DEPARTMENT OF.FOOD AND DRUG ADMINISTRATION.FDA OFFICE OF ACQ  GRANT SVCS</t>
+        </is>
+      </c>
       <c r="L142" s="4" t="inlineStr"/>
       <c r="M142" s="4" t="inlineStr"/>
       <c r="N142" s="4" t="inlineStr">
@@ -25805,17 +25661,17 @@
       </c>
       <c r="O142" s="4" t="inlineStr">
         <is>
-          <t>8f8ea644341143e4b0365947421d57fc</t>
+          <t>7b57c68cd1c94196a4bc7d87b7824706</t>
         </is>
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -25833,17 +25689,17 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Teledyne Griffin G510X Service Agreement</t>
+          <t>Seeking Competitive Lease Proposals – Administrative Office Space in in Atlanta, GA - Request for Lease Proposals No. 26NAT02</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/7b57c68cd1c94196a4bc7d87b7824706/view</t>
+          <t>https://sam.gov/opp/2c0d0e2b4a4e426499999ad8d14e3bc3/view</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>Forensic</t>
+          <t>IRS</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
@@ -25853,18 +25709,18 @@
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T19:00:00+00:00</t>
+          <t>2026-10-08T00:00:00+00:00</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>75F40126Q00370</t>
+          <t>6GA0317</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr"/>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>HEALTH AND HUMAN SERVICES, DEPARTMENT OF.FOOD AND DRUG ADMINISTRATION.FDA OFFICE OF ACQ  GRANT SVCS</t>
+          <t>GENERAL SERVICES ADMINISTRATION.PUBLIC BUILDINGS SERVICE.PBS R00 OFFICE OF LEASING</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr"/>
@@ -25876,7 +25732,7 @@
       </c>
       <c r="O143" s="4" t="inlineStr">
         <is>
-          <t>7b57c68cd1c94196a4bc7d87b7824706</t>
+          <t>2c0d0e2b4a4e426499999ad8d14e3bc3</t>
         </is>
       </c>
       <c r="P143" s="4" t="inlineStr">
@@ -25886,7 +25742,7 @@
       </c>
       <c r="Q143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -25904,12 +25760,12 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Seeking Competitive Lease Proposals – Administrative Office Space in in Atlanta, GA - Request for Lease Proposals No. 26NAT02</t>
+          <t>General Services Administration (GSA) Seeks to lease the following space: Solicitation No. 5TN0238</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/2c0d0e2b4a4e426499999ad8d14e3bc3/view</t>
+          <t>https://sam.gov/opp/99c3844c8d2248a38bee40b24bded882/view</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
@@ -25919,17 +25775,17 @@
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>Combined Synopsis/Solicitation</t>
+          <t>Presolicitation</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:00:00+00:00</t>
+          <t>2026-10-12T21:00:00+00:00</t>
         </is>
       </c>
       <c r="I144" s="4" t="inlineStr">
         <is>
-          <t>6GA0317</t>
+          <t>5TN0238</t>
         </is>
       </c>
       <c r="J144" s="4" t="inlineStr"/>
@@ -25947,7 +25803,7 @@
       </c>
       <c r="O144" s="4" t="inlineStr">
         <is>
-          <t>2c0d0e2b4a4e426499999ad8d14e3bc3</t>
+          <t>99c3844c8d2248a38bee40b24bded882</t>
         </is>
       </c>
       <c r="P144" s="4" t="inlineStr">
@@ -25957,56 +25813,56 @@
       </c>
       <c r="Q144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr"/>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>General Services Administration (GSA) Seeks to lease the following space: Solicitation No. 5TN0238</t>
+          <t>321 STS - DC2 COMM KLAS Equipment</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/99c3844c8d2248a38bee40b24bded882/view</t>
+          <t>https://sam.gov/opp/e817b643cc784f19929ea53259a1d68a/view</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>DC3</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00+00:00</t>
+          <t>2026-09-23T14:00:00+00:00</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>5TN0238</t>
+          <t>FA558726Q0064</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr"/>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>GENERAL SERVICES ADMINISTRATION.PUBLIC BUILDINGS SERVICE.PBS R00 OFFICE OF LEASING</t>
+          <t>DEPT OF DEFENSE.DEPT OF THE AIR FORCE.U.S. AIR FORCES IN EUROPE.FA5587  48 CONS</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr"/>
@@ -26018,45 +25874,45 @@
       </c>
       <c r="O145" s="4" t="inlineStr">
         <is>
-          <t>99c3844c8d2248a38bee40b24bded882</t>
+          <t>e817b643cc784f19929ea53259a1d68a</t>
         </is>
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="Q145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr"/>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Ball Bearings</t>
+          <t>Steritest Symbio ISL 2 System Pump-Brand Name and Equal (BNE)</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/0c69761d169749fea4a45bc5ac38cce9/view</t>
+          <t>https://sam.gov/opp/78e32a5abb1b45ab97ed346514f1fd8e/view</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>Forensic</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
@@ -26066,18 +25922,18 @@
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T17:00:00+00:00</t>
+          <t>2026-09-22T20:00:00+00:00</t>
         </is>
       </c>
       <c r="I146" s="4" t="inlineStr">
         <is>
-          <t>W5119TC26QBAL1</t>
+          <t>FDA-RFQ-OC-2026-134494</t>
         </is>
       </c>
       <c r="J146" s="4" t="inlineStr"/>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>DEPT OF DEFENSE.DEPT OF THE ARMY.AMC.ACC.ACC-CTRS.ACC RI.W6QK ACC-RI</t>
+          <t>HEALTH AND HUMAN SERVICES, DEPARTMENT OF.FOOD AND DRUG ADMINISTRATION.FDA OFFICE OF ACQ  GRANT SVCS</t>
         </is>
       </c>
       <c r="L146" s="4" t="inlineStr"/>
@@ -26089,17 +25945,17 @@
       </c>
       <c r="O146" s="4" t="inlineStr">
         <is>
-          <t>0c69761d169749fea4a45bc5ac38cce9</t>
+          <t>78e32a5abb1b45ab97ed346514f1fd8e</t>
         </is>
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="Q146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -26112,43 +25968,43 @@
       <c r="B147" s="4" t="inlineStr"/>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>321 STS - DC2 COMM KLAS Equipment</t>
+          <t>Remote Support Solution, On-Premise</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/e817b643cc784f19929ea53259a1d68a/view</t>
+          <t>https://sam.gov/opp/4d76dcafca1d4293b37bc133df4bcf1f/view</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>DC3</t>
+          <t>IRS</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>Solicitation</t>
+          <t>Sources Sought</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T14:00:00+00:00</t>
+          <t>2026-09-28T16:00:00+00:00</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>FA558726Q0064</t>
+          <t>IRSWV</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr"/>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>DEPT OF DEFENSE.DEPT OF THE AIR FORCE.U.S. AIR FORCES IN EUROPE.FA5587  48 CONS</t>
+          <t>TREASURY, DEPARTMENT OF THE.INTERNAL REVENUE SERVICE.NATIONAL OFFICE - PROCUREMENT OITA</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr"/>
@@ -26160,7 +26016,7 @@
       </c>
       <c r="O147" s="4" t="inlineStr">
         <is>
-          <t>e817b643cc784f19929ea53259a1d68a</t>
+          <t>4d76dcafca1d4293b37bc133df4bcf1f</t>
         </is>
       </c>
       <c r="P147" s="4" t="inlineStr">
@@ -26170,7 +26026,7 @@
       </c>
       <c r="Q147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -26188,38 +26044,38 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Steritest Symbio ISL 2 System Pump-Brand Name and Equal (BNE)</t>
+          <t>General Services Administration (GSA) seeks to lease office space in Campbell, CA</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/78e32a5abb1b45ab97ed346514f1fd8e/view</t>
+          <t>https://sam.gov/opp/25311fb4aa7a49828c0299b98888d228/view</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>Forensic</t>
+          <t>IRS</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>Combined Synopsis/Solicitation</t>
+          <t>Presolicitation</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T20:00:00+00:00</t>
+          <t>2026-10-03T00:00:00+00:00</t>
         </is>
       </c>
       <c r="I148" s="4" t="inlineStr">
         <is>
-          <t>FDA-RFQ-OC-2026-134494</t>
+          <t>1CA2956A</t>
         </is>
       </c>
       <c r="J148" s="4" t="inlineStr"/>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>HEALTH AND HUMAN SERVICES, DEPARTMENT OF.FOOD AND DRUG ADMINISTRATION.FDA OFFICE OF ACQ  GRANT SVCS</t>
+          <t>GENERAL SERVICES ADMINISTRATION.PUBLIC BUILDINGS SERVICE.PBS R00 CENTER FOR BROKER SERVICES</t>
         </is>
       </c>
       <c r="L148" s="4" t="inlineStr"/>
@@ -26231,7 +26087,7 @@
       </c>
       <c r="O148" s="4" t="inlineStr">
         <is>
-          <t>78e32a5abb1b45ab97ed346514f1fd8e</t>
+          <t>25311fb4aa7a49828c0299b98888d228</t>
         </is>
       </c>
       <c r="P148" s="4" t="inlineStr">
@@ -26259,42 +26115,42 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Remote Support Solution, On-Premise</t>
+          <t>Faraday Room</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/4d76dcafca1d4293b37bc133df4bcf1f/view</t>
+          <t>https://sam.gov/opp/489bb2eed30d4961905c726ceb77cd0a/view</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>Cyber; Forensic; Forensics</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>Sources Sought</t>
-        </is>
-      </c>
-      <c r="H149" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28T16:00:00+00:00</t>
-        </is>
-      </c>
+          <t>Award Notice</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="inlineStr"/>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>IRSWV</t>
+          <t>70US0926P70092921</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr"/>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>TREASURY, DEPARTMENT OF THE.INTERNAL REVENUE SERVICE.NATIONAL OFFICE - PROCUREMENT OITA</t>
+          <t>HOMELAND SECURITY, DEPARTMENT OF.U.S. SECRET SERVICE.U. S. SECRET SERVICE</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr"/>
-      <c r="M149" s="4" t="inlineStr"/>
+      <c r="M149" s="4" t="inlineStr">
+        <is>
+          <t>FARADAY DEFENSE CORPORATION</t>
+        </is>
+      </c>
       <c r="N149" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -26302,7 +26158,7 @@
       </c>
       <c r="O149" s="4" t="inlineStr">
         <is>
-          <t>4d76dcafca1d4293b37bc133df4bcf1f</t>
+          <t>489bb2eed30d4961905c726ceb77cd0a</t>
         </is>
       </c>
       <c r="P149" s="4" t="inlineStr">
@@ -26312,56 +26168,56 @@
       </c>
       <c r="Q149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr"/>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>General Services Administration (GSA) seeks to lease office space in Campbell, CA</t>
+          <t>Vanquish Neo System and Ion Chromatography system</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/25311fb4aa7a49828c0299b98888d228/view</t>
+          <t>https://sam.gov/opp/88bce0d89f7948c39aeef0d6ca3581d6/view</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>Forensic</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T00:00:00+00:00</t>
+          <t>2026-09-21T14:30:00+00:00</t>
         </is>
       </c>
       <c r="I150" s="4" t="inlineStr">
         <is>
-          <t>1CA2956A</t>
+          <t>75F40126Q000430</t>
         </is>
       </c>
       <c r="J150" s="4" t="inlineStr"/>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>GENERAL SERVICES ADMINISTRATION.PUBLIC BUILDINGS SERVICE.PBS R00 CENTER FOR BROKER SERVICES</t>
+          <t>HEALTH AND HUMAN SERVICES, DEPARTMENT OF.FOOD AND DRUG ADMINISTRATION.FDA OFFICE OF ACQ  GRANT SVCS</t>
         </is>
       </c>
       <c r="L150" s="4" t="inlineStr"/>
@@ -26373,68 +26229,68 @@
       </c>
       <c r="O150" s="4" t="inlineStr">
         <is>
-          <t>25311fb4aa7a49828c0299b98888d228</t>
+          <t>88bce0d89f7948c39aeef0d6ca3581d6</t>
         </is>
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Q150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr"/>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Faraday Room</t>
+          <t>R710--Expert Witness Contract (VA-26-00084567)</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/489bb2eed30d4961905c726ceb77cd0a/view</t>
+          <t>https://sam.gov/opp/5ad966f9e35a4638959165d1d922227d/view</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>Cyber; Forensic; Forensics</t>
+          <t>Forensic</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>Award Notice</t>
+          <t>Justification</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>70US0926P70092921</t>
+          <t>OralWritten</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr"/>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>HOMELAND SECURITY, DEPARTMENT OF.U.S. SECRET SERVICE.U. S. SECRET SERVICE</t>
+          <t>VETERANS AFFAIRS, DEPARTMENT OF.VETERANS AFFAIRS, DEPARTMENT OF.RPO CENTRAL (36C24C)</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr"/>
       <c r="M151" s="4" t="inlineStr">
         <is>
-          <t>FARADAY DEFENSE CORPORATION</t>
+          <t>LITCON GROUP LLC</t>
         </is>
       </c>
       <c r="N151" s="4" t="inlineStr">
@@ -26444,12 +26300,12 @@
       </c>
       <c r="O151" s="4" t="inlineStr">
         <is>
-          <t>489bb2eed30d4961905c726ceb77cd0a</t>
+          <t>5ad966f9e35a4638959165d1d922227d</t>
         </is>
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Q151" s="4" t="inlineStr">
@@ -26461,7 +26317,7 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr"/>
@@ -26472,38 +26328,38 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Vanquish Neo System and Ion Chromatography system</t>
+          <t>Enterprise Data Pipeline Modernization and Data Consumption Services</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/88bce0d89f7948c39aeef0d6ca3581d6/view</t>
+          <t>https://sam.gov/opp/6d4373433c504f7994f117458c9e3f9e/view</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>Forensic</t>
+          <t>IRS</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>Solicitation</t>
+          <t>Sources Sought</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T14:30:00+00:00</t>
+          <t>2026-09-25T18:00:00+00:00</t>
         </is>
       </c>
       <c r="I152" s="4" t="inlineStr">
         <is>
-          <t>75F40126Q000430</t>
+          <t>5000233302</t>
         </is>
       </c>
       <c r="J152" s="4" t="inlineStr"/>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>HEALTH AND HUMAN SERVICES, DEPARTMENT OF.FOOD AND DRUG ADMINISTRATION.FDA OFFICE OF ACQ  GRANT SVCS</t>
+          <t>TREASURY, DEPARTMENT OF THE.INTERNAL REVENUE SERVICE.NATIONAL OFFICE - PROCUREMENT OITA</t>
         </is>
       </c>
       <c r="L152" s="4" t="inlineStr"/>
@@ -26515,12 +26371,12 @@
       </c>
       <c r="O152" s="4" t="inlineStr">
         <is>
-          <t>88bce0d89f7948c39aeef0d6ca3581d6</t>
+          <t>6d4373433c504f7994f117458c9e3f9e</t>
         </is>
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Q152" s="4" t="inlineStr">
@@ -26532,53 +26388,53 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr"/>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>R710--Expert Witness Contract (VA-26-00084567)</t>
+          <t>Joint Commission (JC) Physical Environment (PE) and Emergency Management (EM) Standards Workshop</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/5ad966f9e35a4638959165d1d922227d/view</t>
+          <t>https://sam.gov/opp/02c1cee1eb5f4ca59c1d16d7fd1157cc/view</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>Forensic</t>
+          <t>IRS</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>Justification</t>
-        </is>
-      </c>
-      <c r="H153" s="4" t="inlineStr"/>
+          <t>Combined Synopsis/Solicitation</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30T14:00:00+00:00</t>
+        </is>
+      </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>OralWritten</t>
+          <t>HT940626QE101</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr"/>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>VETERANS AFFAIRS, DEPARTMENT OF.VETERANS AFFAIRS, DEPARTMENT OF.RPO CENTRAL (36C24C)</t>
+          <t>DEPT OF DEFENSE.DEFENSE HEALTH AGENCY (DHA).DEFENSE HEALTH AGENCY</t>
         </is>
       </c>
       <c r="L153" s="4" t="inlineStr"/>
-      <c r="M153" s="4" t="inlineStr">
-        <is>
-          <t>LITCON GROUP LLC</t>
-        </is>
-      </c>
+      <c r="M153" s="4" t="inlineStr"/>
       <c r="N153" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -26586,40 +26442,40 @@
       </c>
       <c r="O153" s="4" t="inlineStr">
         <is>
-          <t>5ad966f9e35a4638959165d1d922227d</t>
+          <t>02c1cee1eb5f4ca59c1d16d7fd1157cc</t>
         </is>
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="Q153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr"/>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Enterprise Data Pipeline Modernization and Data Consumption Services</t>
+          <t>Guard Booth - Austin</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/6d4373433c504f7994f117458c9e3f9e/view</t>
+          <t>https://sam.gov/opp/36baab76b846450c87fe281c6bf31418/view</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
@@ -26629,23 +26485,23 @@
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>Sources Sought</t>
+          <t>Combined Synopsis/Solicitation</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T18:00:00+00:00</t>
+          <t>2026-09-18T14:00:00+00:00</t>
         </is>
       </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
-          <t>5000233302</t>
+          <t>2023H2-26-Q-00056</t>
         </is>
       </c>
       <c r="J154" s="4" t="inlineStr"/>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>TREASURY, DEPARTMENT OF THE.INTERNAL REVENUE SERVICE.NATIONAL OFFICE - PROCUREMENT OITA</t>
+          <t>TREASURY, DEPARTMENT OF THE.INTERNAL REVENUE SERVICE.NATIONAL OFFICE - PROCUREMENT OBO</t>
         </is>
       </c>
       <c r="L154" s="4" t="inlineStr"/>
@@ -26657,17 +26513,17 @@
       </c>
       <c r="O154" s="4" t="inlineStr">
         <is>
-          <t>6d4373433c504f7994f117458c9e3f9e</t>
+          <t>36baab76b846450c87fe281c6bf31418</t>
         </is>
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="Q154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -26685,12 +26541,12 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Joint Commission (JC) Physical Environment (PE) and Emergency Management (EM) Standards Workshop</t>
+          <t>Digital Literacy and Innovation Services</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/02c1cee1eb5f4ca59c1d16d7fd1157cc/view</t>
+          <t>https://sam.gov/opp/10ed95bf7cfb468f881fe2968e7d21c0/view</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
@@ -26700,23 +26556,23 @@
       </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
-          <t>Combined Synopsis/Solicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30T14:00:00+00:00</t>
+          <t>2026-09-19T15:00:00+00:00</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>HT940626QE101</t>
+          <t>PR16214159</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr"/>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>DEPT OF DEFENSE.DEFENSE HEALTH AGENCY (DHA).DEFENSE HEALTH AGENCY</t>
+          <t>STATE, DEPARTMENT OF.STATE, DEPARTMENT OF.AMERICAN CONSULATE CASABLANCA</t>
         </is>
       </c>
       <c r="L155" s="4" t="inlineStr"/>
@@ -26728,7 +26584,7 @@
       </c>
       <c r="O155" s="4" t="inlineStr">
         <is>
-          <t>02c1cee1eb5f4ca59c1d16d7fd1157cc</t>
+          <t>10ed95bf7cfb468f881fe2968e7d21c0</t>
         </is>
       </c>
       <c r="P155" s="4" t="inlineStr">
@@ -26751,43 +26607,43 @@
       <c r="B156" s="4" t="inlineStr"/>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Guard Booth - Austin</t>
+          <t>CODIS Phase III (Specialized Forensics IT Equipment)</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>https://sam.gov/opp/36baab76b846450c87fe281c6bf31418/view</t>
+          <t>https://sam.gov/opp/84847251164f4fc78eabd169a2608e4a/view</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>Forensic; Forensics</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>Combined Synopsis/Solicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T14:00:00+00:00</t>
+          <t>2026-09-30T23:00:00+00:00</t>
         </is>
       </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
-          <t>2023H2-26-Q-00056</t>
+          <t>19AQMM26R0250</t>
         </is>
       </c>
       <c r="J156" s="4" t="inlineStr"/>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>TREASURY, DEPARTMENT OF THE.INTERNAL REVENUE SERVICE.NATIONAL OFFICE - PROCUREMENT OBO</t>
+          <t>STATE, DEPARTMENT OF.STATE, DEPARTMENT OF.ACQUISITIONS - AQM MOMENTUM</t>
         </is>
       </c>
       <c r="L156" s="4" t="inlineStr"/>
@@ -26799,7 +26655,7 @@
       </c>
       <c r="O156" s="4" t="inlineStr">
         <is>
-          <t>36baab76b846450c87fe281c6bf31418</t>
+          <t>84847251164f4fc78eabd169a2608e4a</t>
         </is>
       </c>
       <c r="P156" s="4" t="inlineStr">
@@ -26809,154 +26665,12 @@
       </c>
       <c r="Q156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr"/>
-      <c r="C157" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="D157" s="4" t="inlineStr">
-        <is>
-          <t>Digital Literacy and Innovation Services</t>
-        </is>
-      </c>
-      <c r="E157" s="5" t="inlineStr">
-        <is>
-          <t>https://sam.gov/opp/10ed95bf7cfb468f881fe2968e7d21c0/view</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>IRS</t>
-        </is>
-      </c>
-      <c r="G157" s="4" t="inlineStr">
-        <is>
-          <t>Solicitation</t>
-        </is>
-      </c>
-      <c r="H157" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-19T15:00:00+00:00</t>
-        </is>
-      </c>
-      <c r="I157" s="4" t="inlineStr">
-        <is>
-          <t>PR16214159</t>
-        </is>
-      </c>
-      <c r="J157" s="4" t="inlineStr"/>
-      <c r="K157" s="4" t="inlineStr">
-        <is>
-          <t>STATE, DEPARTMENT OF.STATE, DEPARTMENT OF.AMERICAN CONSULATE CASABLANCA</t>
-        </is>
-      </c>
-      <c r="L157" s="4" t="inlineStr"/>
-      <c r="M157" s="4" t="inlineStr"/>
-      <c r="N157" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O157" s="4" t="inlineStr">
-        <is>
-          <t>10ed95bf7cfb468f881fe2968e7d21c0</t>
-        </is>
-      </c>
-      <c r="P157" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="Q157" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="inlineStr"/>
-      <c r="C158" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="D158" s="4" t="inlineStr">
-        <is>
-          <t>CODIS Phase III (Specialized Forensics IT Equipment)</t>
-        </is>
-      </c>
-      <c r="E158" s="5" t="inlineStr">
-        <is>
-          <t>https://sam.gov/opp/84847251164f4fc78eabd169a2608e4a/view</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>Forensic; Forensics</t>
-        </is>
-      </c>
-      <c r="G158" s="4" t="inlineStr">
-        <is>
-          <t>Solicitation</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-30T23:00:00+00:00</t>
-        </is>
-      </c>
-      <c r="I158" s="4" t="inlineStr">
-        <is>
-          <t>19AQMM26R0250</t>
-        </is>
-      </c>
-      <c r="J158" s="4" t="inlineStr"/>
-      <c r="K158" s="4" t="inlineStr">
-        <is>
-          <t>STATE, DEPARTMENT OF.STATE, DEPARTMENT OF.ACQUISITIONS - AQM MOMENTUM</t>
-        </is>
-      </c>
-      <c r="L158" s="4" t="inlineStr"/>
-      <c r="M158" s="4" t="inlineStr"/>
-      <c r="N158" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O158" s="4" t="inlineStr">
-        <is>
-          <t>84847251164f4fc78eabd169a2608e4a</t>
-        </is>
-      </c>
-      <c r="P158" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="Q158" s="4" t="inlineStr">
-        <is>
           <t>2026-09-28</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q158"/>
+  <autoFilter ref="A1:Q156"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -27113,8 +26827,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId153"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId157"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27196,22 +26908,22 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-11_152459</t>
+          <t>2026-10-12_184410</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
@@ -27234,22 +26946,22 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10_150615</t>
+          <t>2026-10-11_152459</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
@@ -27259,7 +26971,7 @@
         <v>50</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>3</v>
@@ -27272,32 +26984,32 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09_155502</t>
+          <t>2026-10-10_150615</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>24</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>3</v>
@@ -27310,32 +27022,32 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08_161131</t>
+          <t>2026-10-09_155502</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>24</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>3</v>
@@ -27348,32 +27060,32 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07_161051</t>
+          <t>2026-10-08_161131</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
         <v>24</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>3</v>
@@ -27386,32 +27098,32 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06_154501</t>
+          <t>2026-10-07_161051</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>24</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>3</v>
@@ -27424,32 +27136,32 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05_180552</t>
+          <t>2026-10-06_154501</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
         <v>24</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>3</v>
@@ -27462,32 +27174,32 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04_144233</t>
+          <t>2026-10-05_180552</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
         <v>24</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>3</v>
@@ -27500,22 +27212,22 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03_141036</t>
+          <t>2026-10-04_144233</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
@@ -27525,7 +27237,7 @@
         <v>61</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>3</v>
@@ -27538,22 +27250,22 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02_153045</t>
+          <t>2026-10-03_141036</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
@@ -27563,7 +27275,7 @@
         <v>61</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>3</v>
@@ -27576,32 +27288,32 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01_160708</t>
+          <t>2026-10-02_153045</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
         <v>24</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>3</v>
@@ -27614,32 +27326,32 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30_154333</t>
+          <t>2026-10-01_160708</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
         <v>24</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>3</v>
@@ -27652,32 +27364,32 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29_152840</t>
+          <t>2026-09-30_154333</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>66</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>3</v>
@@ -27690,32 +27402,32 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28_172727</t>
+          <t>2026-09-29_152840</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
         <v>23</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>3</v>
@@ -27728,22 +27440,22 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27_143611</t>
+          <t>2026-09-28_172727</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -27753,7 +27465,7 @@
         <v>62</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>3</v>

--- a/docs/v/SAM-daily-latest.xlsx
+++ b/docs/v/SAM-daily-latest.xlsx
@@ -8,14 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Daily Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Day 2026-10-25" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Day 2026-10-26" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="All Notices" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="First Seen By Day" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Run Log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Summary'!$A$1:$E$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Day 2026-10-25'!$A$1:$R$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Day 2026-10-26'!$A$1:$R$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Notices'!$A$1:$R$130</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'First Seen By Day'!$A$1:$R$130</definedName>
   </definedNames>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -534,7 +534,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -544,99 +544,99 @@
         <v>39</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>45</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -646,14 +646,14 @@
         <v>45</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -663,31 +663,31 @@
         <v>45</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -697,38 +697,38 @@
         <v>46</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>4</v>
@@ -738,24 +738,24 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
@@ -899,7 +899,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr"/>
@@ -964,14 +964,14 @@
       </c>
       <c r="R2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr"/>
@@ -1036,14 +1036,14 @@
       </c>
       <c r="R3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr"/>
@@ -1108,14 +1108,14 @@
       </c>
       <c r="R4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr"/>
@@ -1180,14 +1180,14 @@
       </c>
       <c r="R5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr"/>
@@ -1252,14 +1252,14 @@
       </c>
       <c r="R6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr"/>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr"/>
@@ -1396,14 +1396,14 @@
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr"/>
@@ -1468,14 +1468,14 @@
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr"/>
@@ -1536,14 +1536,14 @@
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr"/>
@@ -1608,14 +1608,14 @@
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr"/>
@@ -1680,14 +1680,14 @@
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr"/>
@@ -1748,14 +1748,14 @@
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr"/>
@@ -1820,14 +1820,14 @@
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr"/>
@@ -1892,14 +1892,14 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr"/>
@@ -1964,14 +1964,14 @@
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr"/>
@@ -2036,14 +2036,14 @@
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr"/>
@@ -2108,14 +2108,14 @@
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr"/>
@@ -2180,14 +2180,14 @@
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr"/>
@@ -2252,14 +2252,14 @@
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr"/>
@@ -2324,14 +2324,14 @@
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr"/>
@@ -2396,14 +2396,14 @@
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr"/>
@@ -2468,14 +2468,14 @@
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr"/>
@@ -2540,14 +2540,14 @@
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr"/>
@@ -2612,14 +2612,14 @@
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr"/>
@@ -2684,14 +2684,14 @@
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr"/>
@@ -2756,14 +2756,14 @@
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr"/>
@@ -2828,14 +2828,14 @@
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr"/>
@@ -2900,14 +2900,14 @@
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr"/>
@@ -2972,14 +2972,14 @@
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr"/>
@@ -3044,14 +3044,14 @@
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr"/>
@@ -3116,14 +3116,14 @@
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr"/>
@@ -3188,14 +3188,14 @@
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr"/>
@@ -3260,14 +3260,14 @@
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr"/>
@@ -3332,14 +3332,14 @@
       </c>
       <c r="R35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr"/>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="R36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr"/>
@@ -3476,14 +3476,14 @@
       </c>
       <c r="R37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr"/>
@@ -3548,14 +3548,14 @@
       </c>
       <c r="R38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr"/>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="R39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr"/>
@@ -3692,7 +3692,7 @@
       </c>
       <c r="R40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr"/>
@@ -3932,14 +3932,14 @@
       </c>
       <c r="R2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr"/>
@@ -4004,14 +4004,14 @@
       </c>
       <c r="R3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr"/>
@@ -4076,14 +4076,14 @@
       </c>
       <c r="R4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr"/>
@@ -4148,14 +4148,14 @@
       </c>
       <c r="R5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr"/>
@@ -4220,14 +4220,14 @@
       </c>
       <c r="R6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr"/>
@@ -4292,14 +4292,14 @@
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr"/>
@@ -4364,14 +4364,14 @@
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr"/>
@@ -4436,14 +4436,14 @@
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr"/>
@@ -4508,14 +4508,14 @@
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr"/>
@@ -4576,14 +4576,14 @@
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr"/>
@@ -4648,14 +4648,14 @@
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr"/>
@@ -4720,14 +4720,14 @@
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr"/>
@@ -4788,14 +4788,14 @@
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr"/>
@@ -4860,14 +4860,14 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr"/>
@@ -4932,14 +4932,14 @@
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr"/>
@@ -5004,14 +5004,14 @@
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr"/>
@@ -5076,14 +5076,14 @@
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr"/>
@@ -5148,14 +5148,14 @@
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr"/>
@@ -5220,14 +5220,14 @@
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr"/>
@@ -5292,14 +5292,14 @@
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr"/>
@@ -5364,14 +5364,14 @@
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr"/>
@@ -5436,14 +5436,14 @@
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr"/>
@@ -5508,14 +5508,14 @@
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr"/>
@@ -5580,14 +5580,14 @@
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr"/>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr"/>
@@ -5724,14 +5724,14 @@
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr"/>
@@ -5796,14 +5796,14 @@
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr"/>
@@ -5868,14 +5868,14 @@
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr"/>
@@ -5940,14 +5940,14 @@
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr"/>
@@ -6012,14 +6012,14 @@
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr"/>
@@ -6084,14 +6084,14 @@
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr"/>
@@ -6156,14 +6156,14 @@
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr"/>
@@ -6228,14 +6228,14 @@
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr"/>
@@ -6300,14 +6300,14 @@
       </c>
       <c r="R35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr"/>
@@ -6372,14 +6372,14 @@
       </c>
       <c r="R36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr"/>
@@ -6444,14 +6444,14 @@
       </c>
       <c r="R37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr"/>
@@ -6516,14 +6516,14 @@
       </c>
       <c r="R38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr"/>
@@ -6588,14 +6588,14 @@
       </c>
       <c r="R39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr"/>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="R40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13426,7 +13426,7 @@
       </c>
       <c r="R2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13498,7 +13498,7 @@
       </c>
       <c r="R3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="R4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13642,7 +13642,7 @@
       </c>
       <c r="R5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="R6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13786,7 +13786,7 @@
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13858,7 +13858,7 @@
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13930,7 +13930,7 @@
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14142,7 +14142,7 @@
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14214,7 +14214,7 @@
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14282,7 +14282,7 @@
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14426,7 +14426,7 @@
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14642,7 +14642,7 @@
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14786,7 +14786,7 @@
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14858,7 +14858,7 @@
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14930,7 +14930,7 @@
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15002,7 +15002,7 @@
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15074,7 +15074,7 @@
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15218,7 +15218,7 @@
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15650,7 +15650,7 @@
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15722,7 +15722,7 @@
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15938,7 +15938,7 @@
       </c>
       <c r="R37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16010,7 +16010,7 @@
       </c>
       <c r="R38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="R39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16154,7 +16154,7 @@
       </c>
       <c r="R40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16226,7 +16226,7 @@
       </c>
       <c r="R41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16370,7 +16370,7 @@
       </c>
       <c r="R43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16586,7 +16586,7 @@
       </c>
       <c r="R46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16946,7 +16946,7 @@
       </c>
       <c r="R51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -17662,7 +17662,7 @@
       </c>
       <c r="R61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -18238,7 +18238,7 @@
       </c>
       <c r="R69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -18310,7 +18310,7 @@
       </c>
       <c r="R70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -22807,22 +22807,22 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-25_092210</t>
+          <t>2026-10-26_093449</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
@@ -22845,22 +22845,22 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24_092128</t>
+          <t>2026-10-25_092210</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
@@ -22870,7 +22870,7 @@
         <v>39</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>3</v>
@@ -22883,32 +22883,32 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23_092806</t>
+          <t>2026-10-24_092128</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>29</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>3</v>
@@ -22921,32 +22921,32 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22_092931</t>
+          <t>2026-10-23_092806</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>29</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>3</v>
@@ -22959,32 +22959,32 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21_092743</t>
+          <t>2026-10-22_092931</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
         <v>29</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>3</v>
@@ -22997,7 +22997,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21_012830</t>
+          <t>2026-10-21_092743</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -23022,7 +23022,7 @@
         <v>42</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>3</v>
@@ -23035,32 +23035,32 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20_162138</t>
+          <t>2026-10-21_012830</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
         <v>29</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>3</v>
@@ -23073,7 +23073,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20_141035</t>
+          <t>2026-10-20_162138</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -23092,13 +23092,13 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>3</v>
@@ -23111,32 +23111,32 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19_161731</t>
+          <t>2026-10-20_141035</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
         <v>24</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>3</v>
@@ -23149,22 +23149,22 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-18_130358</t>
+          <t>2026-10-19_161731</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
@@ -23174,7 +23174,7 @@
         <v>45</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>3</v>
@@ -23187,22 +23187,22 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-17_124531</t>
+          <t>2026-10-18_130358</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
@@ -23212,7 +23212,7 @@
         <v>45</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>3</v>
@@ -23225,32 +23225,32 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16_134806</t>
+          <t>2026-10-17_124531</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
         <v>24</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>3</v>
@@ -23263,22 +23263,22 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15_140128</t>
+          <t>2026-10-16_134806</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
@@ -23288,7 +23288,7 @@
         <v>46</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>3</v>
@@ -23301,32 +23301,32 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_142359</t>
+          <t>2026-10-15_140128</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
         <v>24</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>3</v>
@@ -23339,29 +23339,29 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13_164653</t>
+          <t>2026-10-14_142359</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
         <v>24</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>4</v>
@@ -23377,32 +23377,32 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12_184410</t>
+          <t>2026-10-13_164653</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>24</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>3</v>
@@ -23415,22 +23415,22 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-11_152459</t>
+          <t>2026-10-12_184410</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
